--- a/currentbuild/StructureDefinition-ChildOrganization.xlsx
+++ b/currentbuild/StructureDefinition-ChildOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-12T11:23:40+00:00</t>
+    <t>2023-02-13T09:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
